--- a/docs/Frontend_Module_Coverage.xlsx
+++ b/docs/Frontend_Module_Coverage.xlsx
@@ -96,7 +96,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -121,8 +121,8 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>(COUNTIF(F5:F42,"Yes")+0.5*COUNTIF(F5:F42,"Partial"))/38</f>
-        <v>0.131579</v>
+        <f>(COUNTIF(F5:F44,"Yes")+0.5*COUNTIF(F5:F44,"Partial"))/40</f>
+        <v>0.137500</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
@@ -130,8 +130,8 @@
         </is>
       </c>
       <c r="E2" s="5">
-        <f>COUNTIF(F5:F42,"Yes")</f>
-        <v>4</v>
+        <f>COUNTIF(F5:F44,"Yes")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
@@ -149,8 +149,8 @@
         </is>
       </c>
       <c r="E3" s="5">
-        <f>COUNTIF(F5:F42,"Partial")</f>
-        <v>2</v>
+        <f>COUNTIF(F5:F44,"Partial")</f>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -158,8 +158,8 @@
         </is>
       </c>
       <c r="G3" s="5">
-        <f>COUNTIF(F5:F42,"No")</f>
-        <v>32</v>
+        <f>COUNTIF(F5:F44,"No")</f>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settings (Business Setup · Appearance · Login · Security)</t>
+          <t xml:space="preserve">Settings (Business Setup · Money · Operations · Comms · Integrations)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Org, App Shell, Login</t>
+          <t xml:space="preserve">Org, IAM, Help Center, Storefront Studio, App Shell, Login</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Appearance + Login editor built; business/security/custom-fields/numbering/roles to build.</t>
+          <t xml:space="preserve">Full module: landing grid + Business Setup, Currencies/FX, Tax, Doc Numbering, Custom Fields, Pipelines, Gateways, Bank Accounts, Email Signatures, Document Templates, Notifications, Scheduled Reports, API Keys/Secrets, Businesses. Audit→IAM; Roles→Org; Policies→Studio.</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1526,76 @@
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Action catalogue, guardrails (6.31).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IAM &amp; Security</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/iam-security</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settings, Org, Login</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audit log (moved here from Settings), security events, sessions, access reviews. Scope TBD; placeholder landing built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help Center</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/help</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settings, App Shell</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB-driven guides &amp; FAQs (mirrors hub-system help-editor). Placeholder landing built.</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1604,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F44">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>
